--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_nuble.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:29</t>
+    <t xml:space="preserve">2026-09-24 01:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0.2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.13</v>
@@ -759,13 +759,13 @@
         <v>19</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="12">
@@ -785,10 +785,10 @@
         <v>0.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="13">
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="14">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_nuble.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:19</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2021_nuble.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-05 19:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -650,7 +650,7 @@
         <v>326</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="7">
@@ -776,7 +776,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>19</v>
